--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,122 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122382773</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97129</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Älgmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593105</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6573247</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,11 +926,6 @@
       </c>
       <c r="E4" t="n">
         <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,6 +926,11 @@
       </c>
       <c r="E4" t="n">
         <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122382773</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84572491</v>
+        <v>122382773</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +704,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olstorp, N om, Srm</t>
+          <t>Älgmossen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593408.1538155507</v>
+        <v>593105</v>
       </c>
       <c r="R2" t="n">
-        <v>6573163.155880502</v>
+        <v>6573247</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,20 +771,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +789,7 @@
         <v>84572490</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593397.9197985232</v>
+        <v>593398</v>
       </c>
       <c r="R3" t="n">
-        <v>6573162.904040528</v>
+        <v>6573163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +854,9 @@
           <t>2020-04-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382773</v>
+        <v>84572491</v>
       </c>
       <c r="B4" t="n">
-        <v>97198</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +899,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,23 +917,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmossen, Srm</t>
+          <t>Olstorp, N om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593105</v>
+        <v>593408</v>
       </c>
       <c r="R4" t="n">
-        <v>6573247</v>
+        <v>6573163</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2020-04-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2020-04-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,15 +970,20 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 62009-2024 artfynd.xlsx
+++ b/artfynd/A 62009-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122382773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84572490</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84572491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>